--- a/Unity/Assets/Config/Excel/EquipConfig.xlsx
+++ b/Unity/Assets/Config/Excel/EquipConfig.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="26">
   <si>
     <t>装备ID</t>
   </si>
@@ -34,9 +34,6 @@
     <t>效果数值, int 属性等于原来值，float 值 * 10000</t>
   </si>
   <si>
-    <t>Buff触发条件</t>
-  </si>
-  <si>
     <t>装备的附加效果，如减速，元素</t>
   </si>
   <si>
@@ -59,9 +56,6 @@
   </si>
   <si>
     <t>EffectValues</t>
-  </si>
-  <si>
-    <t>BuffCondition</t>
   </si>
   <si>
     <t>BuffIds</t>
@@ -1389,7 +1383,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:K12"/>
+  <dimension ref="A1:J12"/>
   <sheetFormatPr defaultColWidth="6" defaultRowHeight="14.25" customHeight="1" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col min="1" max="1" width="14.1719" style="1" customWidth="1"/>
@@ -1398,9 +1392,8 @@
     <col min="5" max="5" width="15.3516" style="1" customWidth="1"/>
     <col min="6" max="8" width="10.3516" style="1" customWidth="1"/>
     <col min="9" max="9" width="17.5" style="1" customWidth="1"/>
-    <col min="10" max="10" width="14" style="1" customWidth="1"/>
-    <col min="11" max="11" width="24.6719" style="1" customWidth="1"/>
-    <col min="12" max="16384" width="6" style="1" customWidth="1"/>
+    <col min="10" max="10" width="24.6719" style="1" customWidth="1"/>
+    <col min="11" max="16384" width="6" style="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="14" customHeight="1">
@@ -1414,7 +1407,6 @@
       <c r="H1" s="2"/>
       <c r="I1" s="2"/>
       <c r="J1" s="2"/>
-      <c r="K1" s="2"/>
     </row>
     <row r="2" ht="14" customHeight="1">
       <c r="A2" s="2"/>
@@ -1427,7 +1419,6 @@
       <c r="H2" s="4"/>
       <c r="I2" s="4"/>
       <c r="J2" s="4"/>
-      <c r="K2" s="4"/>
     </row>
     <row r="3" ht="15" customHeight="1">
       <c r="A3" s="2"/>
@@ -1456,70 +1447,61 @@
       <c r="J3" t="s" s="8">
         <v>7</v>
       </c>
-      <c r="K3" t="s" s="8">
-        <v>8</v>
-      </c>
     </row>
     <row r="4" ht="14" customHeight="1">
       <c r="A4" s="9"/>
       <c r="B4" s="10"/>
       <c r="C4" t="s" s="6">
+        <v>8</v>
+      </c>
+      <c r="D4" t="s" s="6">
         <v>9</v>
       </c>
-      <c r="D4" t="s" s="6">
+      <c r="E4" t="s" s="11">
         <v>10</v>
       </c>
-      <c r="E4" t="s" s="11">
+      <c r="F4" t="s" s="8">
         <v>11</v>
       </c>
-      <c r="F4" t="s" s="8">
+      <c r="G4" t="s" s="8">
         <v>12</v>
       </c>
-      <c r="G4" t="s" s="8">
+      <c r="H4" t="s" s="8">
         <v>13</v>
       </c>
-      <c r="H4" t="s" s="8">
+      <c r="I4" t="s" s="8">
         <v>14</v>
       </c>
-      <c r="I4" t="s" s="8">
+      <c r="J4" t="s" s="8">
         <v>15</v>
-      </c>
-      <c r="J4" t="s" s="8">
-        <v>16</v>
-      </c>
-      <c r="K4" t="s" s="8">
-        <v>17</v>
       </c>
     </row>
     <row r="5" ht="14" customHeight="1">
       <c r="A5" s="2"/>
       <c r="B5" s="5"/>
       <c r="C5" t="s" s="6">
+        <v>16</v>
+      </c>
+      <c r="D5" t="s" s="6">
+        <v>17</v>
+      </c>
+      <c r="E5" t="s" s="7">
+        <v>17</v>
+      </c>
+      <c r="F5" t="s" s="12">
+        <v>16</v>
+      </c>
+      <c r="G5" t="s" s="12">
+        <v>16</v>
+      </c>
+      <c r="H5" t="s" s="12">
         <v>18</v>
       </c>
-      <c r="D5" t="s" s="6">
-        <v>19</v>
-      </c>
-      <c r="E5" t="s" s="7">
-        <v>19</v>
-      </c>
-      <c r="F5" t="s" s="12">
+      <c r="I5" t="s" s="12">
         <v>18</v>
-      </c>
-      <c r="G5" t="s" s="12">
-        <v>18</v>
-      </c>
-      <c r="H5" t="s" s="12">
-        <v>20</v>
-      </c>
-      <c r="I5" t="s" s="12">
-        <v>20</v>
       </c>
       <c r="J5" t="s" s="12">
         <v>18</v>
-      </c>
-      <c r="K5" t="s" s="12">
-        <v>20</v>
       </c>
     </row>
     <row r="6" ht="16" customHeight="1">
@@ -1529,10 +1511,10 @@
         <v>1</v>
       </c>
       <c r="D6" t="s" s="14">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="E6" t="s" s="14">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="F6" s="13">
         <v>1</v>
@@ -1546,10 +1528,7 @@
       <c r="I6" s="13">
         <v>100</v>
       </c>
-      <c r="J6" s="13">
-        <v>0</v>
-      </c>
-      <c r="K6" s="15"/>
+      <c r="J6" s="15"/>
     </row>
     <row r="7" ht="16" customHeight="1">
       <c r="A7" s="2"/>
@@ -1558,10 +1537,10 @@
         <v>2</v>
       </c>
       <c r="D7" t="s" s="17">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="E7" t="s" s="17">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="F7" s="16">
         <v>2</v>
@@ -1575,10 +1554,7 @@
       <c r="I7" s="16">
         <v>100</v>
       </c>
-      <c r="J7" s="16">
-        <v>0</v>
-      </c>
-      <c r="K7" s="2"/>
+      <c r="J7" s="2"/>
     </row>
     <row r="8" ht="16" customHeight="1">
       <c r="A8" s="2"/>
@@ -1587,10 +1563,10 @@
         <v>3</v>
       </c>
       <c r="D8" t="s" s="17">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="E8" t="s" s="17">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="F8" s="16">
         <v>3</v>
@@ -1604,10 +1580,7 @@
       <c r="I8" s="16">
         <v>50</v>
       </c>
-      <c r="J8" s="16">
-        <v>0</v>
-      </c>
-      <c r="K8" s="2"/>
+      <c r="J8" s="2"/>
     </row>
     <row r="9" ht="14" customHeight="1">
       <c r="A9" s="2"/>
@@ -1616,10 +1589,10 @@
         <v>4</v>
       </c>
       <c r="D9" t="s" s="17">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="E9" t="s" s="17">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="F9" s="16">
         <v>4</v>
@@ -1633,10 +1606,7 @@
       <c r="I9" s="16">
         <v>100</v>
       </c>
-      <c r="J9" s="16">
-        <v>0</v>
-      </c>
-      <c r="K9" s="2"/>
+      <c r="J9" s="2"/>
     </row>
     <row r="10" ht="14" customHeight="1">
       <c r="A10" s="2"/>
@@ -1645,10 +1615,10 @@
         <v>5</v>
       </c>
       <c r="D10" t="s" s="17">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="E10" t="s" s="17">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="F10" s="16">
         <v>5</v>
@@ -1662,10 +1632,7 @@
       <c r="I10" s="16">
         <v>100</v>
       </c>
-      <c r="J10" s="16">
-        <v>0</v>
-      </c>
-      <c r="K10" s="2"/>
+      <c r="J10" s="2"/>
     </row>
     <row r="11" ht="14" customHeight="1">
       <c r="A11" s="2"/>
@@ -1674,10 +1641,10 @@
         <v>6</v>
       </c>
       <c r="D11" t="s" s="17">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="E11" t="s" s="17">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="F11" s="16">
         <v>6</v>
@@ -1691,10 +1658,7 @@
       <c r="I11" s="16">
         <v>50</v>
       </c>
-      <c r="J11" s="16">
-        <v>0</v>
-      </c>
-      <c r="K11" s="2"/>
+      <c r="J11" s="2"/>
     </row>
     <row r="12" ht="14" customHeight="1">
       <c r="A12" s="2"/>
@@ -1703,10 +1667,10 @@
         <v>7</v>
       </c>
       <c r="D12" t="s" s="17">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="E12" t="s" s="17">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="F12" s="16">
         <v>7</v>
@@ -1720,10 +1684,7 @@
       <c r="I12" s="16">
         <v>50</v>
       </c>
-      <c r="J12" s="16">
-        <v>0</v>
-      </c>
-      <c r="K12" s="2"/>
+      <c r="J12" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.699306" right="0.699306" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Unity/Assets/Config/Excel/EquipConfig.xlsx
+++ b/Unity/Assets/Config/Excel/EquipConfig.xlsx
@@ -46,7 +46,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>EquiqType</t>
+    <t>EquipType</t>
   </si>
   <si>
     <t>Slot</t>
@@ -55,7 +55,7 @@
     <t>Numerics</t>
   </si>
   <si>
-    <t>EffectValues</t>
+    <t>NumericValues</t>
   </si>
   <si>
     <t>BuffIds</t>
@@ -1391,7 +1391,7 @@
     <col min="4" max="4" width="10.1719" style="1" customWidth="1"/>
     <col min="5" max="5" width="15.3516" style="1" customWidth="1"/>
     <col min="6" max="8" width="10.3516" style="1" customWidth="1"/>
-    <col min="9" max="9" width="17.5" style="1" customWidth="1"/>
+    <col min="9" max="9" width="20.625" style="1" customWidth="1"/>
     <col min="10" max="10" width="24.6719" style="1" customWidth="1"/>
     <col min="11" max="16384" width="6" style="1" customWidth="1"/>
   </cols>

--- a/Unity/Assets/Config/Excel/EquipConfig.xlsx
+++ b/Unity/Assets/Config/Excel/EquipConfig.xlsx
@@ -52,10 +52,10 @@
     <t>Slot</t>
   </si>
   <si>
-    <t>Numerics</t>
-  </si>
-  <si>
-    <t>NumericValues</t>
+    <t>Attributes</t>
+  </si>
+  <si>
+    <t>AttributeValues</t>
   </si>
   <si>
     <t>BuffIds</t>
